--- a/backend/data/financials_by_company/1448.HK.xlsx
+++ b/backend/data/financials_by_company/1448.HK.xlsx
@@ -682,622 +682,622 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-13152683.139854</v>
+        <v>5798958</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3864</v>
+        <v>0.246</v>
       </c>
       <c r="D2" t="n">
-        <v>1034149000</v>
+        <v>1309642000</v>
       </c>
       <c r="E2" t="n">
-        <v>-34039000</v>
+        <v>23573000</v>
       </c>
       <c r="F2" t="n">
-        <v>-34039000</v>
+        <v>23573000</v>
       </c>
       <c r="G2" t="n">
-        <v>373134000</v>
+        <v>720033000</v>
       </c>
       <c r="H2" t="n">
-        <v>173179000</v>
+        <v>146734000</v>
       </c>
       <c r="I2" t="n">
-        <v>694828000</v>
+        <v>786064000</v>
       </c>
       <c r="J2" t="n">
-        <v>1000110000</v>
+        <v>1333215000</v>
       </c>
       <c r="K2" t="n">
-        <v>826931000</v>
+        <v>1186481000</v>
       </c>
       <c r="L2" t="n">
-        <v>5389000</v>
+        <v>7623000</v>
       </c>
       <c r="M2" t="n">
-        <v>16422000</v>
+        <v>7246000</v>
       </c>
       <c r="N2" t="n">
-        <v>21811000</v>
+        <v>14869000</v>
       </c>
       <c r="O2" t="n">
-        <v>394020316.860146</v>
+        <v>702258958</v>
       </c>
       <c r="P2" t="n">
-        <v>373134000</v>
+        <v>720033000</v>
       </c>
       <c r="Q2" t="n">
-        <v>1212364000</v>
+        <v>1193681000</v>
       </c>
       <c r="R2" t="n">
-        <v>709887000</v>
+        <v>1094478000</v>
       </c>
       <c r="S2" t="n">
-        <v>2271063422</v>
+        <v>2278585161</v>
       </c>
       <c r="T2" t="n">
-        <v>2271063422</v>
+        <v>2278490319</v>
       </c>
       <c r="U2" t="n">
-        <v>0.164</v>
+        <v>0.316</v>
       </c>
       <c r="V2" t="n">
-        <v>0.164</v>
+        <v>0.316</v>
       </c>
       <c r="W2" t="n">
-        <v>373134000</v>
+        <v>720033000</v>
       </c>
       <c r="X2" t="n">
-        <v>373134000</v>
+        <v>720033000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>373134000</v>
+        <v>720033000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-124194000</v>
+        <v>-169611000</v>
       </c>
       <c r="AB2" t="n">
-        <v>497328000</v>
+        <v>889644000</v>
       </c>
       <c r="AC2" t="n">
-        <v>497328000</v>
+        <v>889644000</v>
       </c>
       <c r="AD2" t="n">
-        <v>313181000</v>
+        <v>289591000</v>
       </c>
       <c r="AE2" t="n">
-        <v>810509000</v>
+        <v>1179235000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-8123000</v>
+        <v>30722000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-78792000</v>
+        <v>-4393000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-48986000</v>
+        <v>572000</v>
       </c>
       <c r="AI2" t="n">
-        <v>23585000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>104193000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>3821000</v>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
       <c r="AL2" t="n">
-        <v>5389000</v>
+        <v>7623000</v>
       </c>
       <c r="AM2" t="n">
-        <v>16422000</v>
+        <v>7246000</v>
       </c>
       <c r="AN2" t="n">
-        <v>21811000</v>
+        <v>14869000</v>
       </c>
       <c r="AO2" t="n">
-        <v>865120000</v>
+        <v>1132167000</v>
       </c>
       <c r="AP2" t="n">
-        <v>517536000</v>
+        <v>407617000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>51111000</v>
+        <v>53122000</v>
       </c>
       <c r="AR2" t="n">
-        <v>173179000</v>
+        <v>146734000</v>
       </c>
       <c r="AS2" t="n">
-        <v>173179000</v>
+        <v>146734000</v>
       </c>
       <c r="AT2" t="n">
-        <v>285973000</v>
+        <v>241629000</v>
       </c>
       <c r="AU2" t="n">
-        <v>41597000</v>
+        <v>43986000</v>
       </c>
       <c r="AV2" t="n">
-        <v>244376000</v>
+        <v>197643000</v>
       </c>
       <c r="AW2" t="n">
-        <v>1382656000</v>
+        <v>1539784000</v>
       </c>
       <c r="AX2" t="n">
-        <v>694828000</v>
+        <v>786064000</v>
       </c>
       <c r="AY2" t="n">
-        <v>2077484000</v>
+        <v>2325848000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2077484000</v>
+        <v>2325848000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>15390848.775526</v>
+        <v>2711661.704533</v>
       </c>
       <c r="C3" t="n">
-        <v>0.318282</v>
+        <v>0.257714</v>
       </c>
       <c r="D3" t="n">
-        <v>1557199000</v>
+        <v>1242644000</v>
       </c>
       <c r="E3" t="n">
-        <v>48356000</v>
+        <v>10522000</v>
       </c>
       <c r="F3" t="n">
-        <v>48356000</v>
+        <v>10522000</v>
       </c>
       <c r="G3" t="n">
-        <v>791240000</v>
+        <v>658596000</v>
       </c>
       <c r="H3" t="n">
-        <v>166609000</v>
+        <v>155953000</v>
       </c>
       <c r="I3" t="n">
-        <v>772679000</v>
+        <v>694263000</v>
       </c>
       <c r="J3" t="n">
-        <v>1605555000</v>
+        <v>1253166000</v>
       </c>
       <c r="K3" t="n">
-        <v>1438946000</v>
+        <v>1097213000</v>
       </c>
       <c r="L3" t="n">
-        <v>9949000</v>
+        <v>8715000</v>
       </c>
       <c r="M3" t="n">
-        <v>7392000</v>
+        <v>5008000</v>
       </c>
       <c r="N3" t="n">
-        <v>17341000</v>
+        <v>13723000</v>
       </c>
       <c r="O3" t="n">
-        <v>758274848.775526</v>
+        <v>650785661.704533</v>
       </c>
       <c r="P3" t="n">
-        <v>791240000</v>
+        <v>658596000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1226041000</v>
+        <v>1113464000</v>
       </c>
       <c r="R3" t="n">
-        <v>1372199000</v>
+        <v>1030327000</v>
       </c>
       <c r="S3" t="n">
-        <v>2271063422</v>
+        <v>2271451099</v>
       </c>
       <c r="T3" t="n">
-        <v>2271063422</v>
+        <v>2271451099</v>
       </c>
       <c r="U3" t="n">
-        <v>0.348</v>
+        <v>0.29</v>
       </c>
       <c r="V3" t="n">
-        <v>0.348</v>
+        <v>0.29</v>
       </c>
       <c r="W3" t="n">
-        <v>791240000</v>
+        <v>658596000</v>
       </c>
       <c r="X3" t="n">
-        <v>791240000</v>
+        <v>658596000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>791240000</v>
+        <v>658596000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-184676000</v>
+        <v>-152133000</v>
       </c>
       <c r="AB3" t="n">
-        <v>975916000</v>
+        <v>810729000</v>
       </c>
       <c r="AC3" t="n">
-        <v>975916000</v>
+        <v>810729000</v>
       </c>
       <c r="AD3" t="n">
-        <v>455638000</v>
+        <v>281476000</v>
       </c>
       <c r="AE3" t="n">
-        <v>1431554000</v>
+        <v>1092205000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-11543000</v>
+        <v>11130000</v>
       </c>
       <c r="AG3" t="n">
-        <v>8689000</v>
+        <v>-20052000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-8648000</v>
+        <v>18814000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-41000</v>
+        <v>1238000</v>
       </c>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>9949000</v>
+        <v>8715000</v>
       </c>
       <c r="AM3" t="n">
-        <v>7392000</v>
+        <v>5008000</v>
       </c>
       <c r="AN3" t="n">
-        <v>17341000</v>
+        <v>13723000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1401988000</v>
+        <v>1058162000</v>
       </c>
       <c r="AP3" t="n">
-        <v>453362000</v>
+        <v>419201000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>62160000</v>
+        <v>55417000</v>
       </c>
       <c r="AR3" t="n">
-        <v>166609000</v>
+        <v>155953000</v>
       </c>
       <c r="AS3" t="n">
-        <v>166609000</v>
+        <v>155953000</v>
       </c>
       <c r="AT3" t="n">
-        <v>220429000</v>
+        <v>196771000</v>
       </c>
       <c r="AU3" t="n">
-        <v>48899000</v>
+        <v>43155000</v>
       </c>
       <c r="AV3" t="n">
-        <v>171530000</v>
+        <v>153616000</v>
       </c>
       <c r="AW3" t="n">
-        <v>1855350000</v>
+        <v>1477363000</v>
       </c>
       <c r="AX3" t="n">
-        <v>772679000</v>
+        <v>694263000</v>
       </c>
       <c r="AY3" t="n">
-        <v>2628029000</v>
+        <v>2171626000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2628029000</v>
+        <v>2171626000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>2711661.704533</v>
+        <v>15390848.775526</v>
       </c>
       <c r="C4" t="n">
-        <v>0.257714</v>
+        <v>0.318282</v>
       </c>
       <c r="D4" t="n">
-        <v>1242644000</v>
+        <v>1557199000</v>
       </c>
       <c r="E4" t="n">
-        <v>10522000</v>
+        <v>48356000</v>
       </c>
       <c r="F4" t="n">
-        <v>10522000</v>
+        <v>48356000</v>
       </c>
       <c r="G4" t="n">
-        <v>658596000</v>
+        <v>791240000</v>
       </c>
       <c r="H4" t="n">
-        <v>155953000</v>
+        <v>166609000</v>
       </c>
       <c r="I4" t="n">
-        <v>694263000</v>
+        <v>772679000</v>
       </c>
       <c r="J4" t="n">
-        <v>1253166000</v>
+        <v>1605555000</v>
       </c>
       <c r="K4" t="n">
-        <v>1097213000</v>
+        <v>1438946000</v>
       </c>
       <c r="L4" t="n">
-        <v>8715000</v>
+        <v>9949000</v>
       </c>
       <c r="M4" t="n">
-        <v>5008000</v>
+        <v>7392000</v>
       </c>
       <c r="N4" t="n">
-        <v>13723000</v>
+        <v>17341000</v>
       </c>
       <c r="O4" t="n">
-        <v>650785661.704533</v>
+        <v>758274848.775526</v>
       </c>
       <c r="P4" t="n">
-        <v>658596000</v>
+        <v>791240000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1113464000</v>
+        <v>1226041000</v>
       </c>
       <c r="R4" t="n">
-        <v>1030327000</v>
+        <v>1372199000</v>
       </c>
       <c r="S4" t="n">
-        <v>2271451099</v>
+        <v>2271063422</v>
       </c>
       <c r="T4" t="n">
-        <v>2271451099</v>
+        <v>2271063422</v>
       </c>
       <c r="U4" t="n">
-        <v>0.29</v>
+        <v>0.348</v>
       </c>
       <c r="V4" t="n">
-        <v>0.29</v>
+        <v>0.348</v>
       </c>
       <c r="W4" t="n">
-        <v>658596000</v>
+        <v>791240000</v>
       </c>
       <c r="X4" t="n">
-        <v>658596000</v>
+        <v>791240000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>658596000</v>
+        <v>791240000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-152133000</v>
+        <v>-184676000</v>
       </c>
       <c r="AB4" t="n">
-        <v>810729000</v>
+        <v>975916000</v>
       </c>
       <c r="AC4" t="n">
-        <v>810729000</v>
+        <v>975916000</v>
       </c>
       <c r="AD4" t="n">
-        <v>281476000</v>
+        <v>455638000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1092205000</v>
+        <v>1431554000</v>
       </c>
       <c r="AF4" t="n">
-        <v>11130000</v>
+        <v>-11543000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-20052000</v>
+        <v>8689000</v>
       </c>
       <c r="AH4" t="n">
-        <v>18814000</v>
+        <v>-8648000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1238000</v>
+        <v>-41000</v>
       </c>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>8715000</v>
+        <v>9949000</v>
       </c>
       <c r="AM4" t="n">
-        <v>5008000</v>
+        <v>7392000</v>
       </c>
       <c r="AN4" t="n">
-        <v>13723000</v>
+        <v>17341000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1058162000</v>
+        <v>1401988000</v>
       </c>
       <c r="AP4" t="n">
-        <v>419201000</v>
+        <v>453362000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>55417000</v>
+        <v>62160000</v>
       </c>
       <c r="AR4" t="n">
-        <v>155953000</v>
+        <v>166609000</v>
       </c>
       <c r="AS4" t="n">
-        <v>155953000</v>
+        <v>166609000</v>
       </c>
       <c r="AT4" t="n">
-        <v>196771000</v>
+        <v>220429000</v>
       </c>
       <c r="AU4" t="n">
-        <v>43155000</v>
+        <v>48899000</v>
       </c>
       <c r="AV4" t="n">
-        <v>153616000</v>
+        <v>171530000</v>
       </c>
       <c r="AW4" t="n">
-        <v>1477363000</v>
+        <v>1855350000</v>
       </c>
       <c r="AX4" t="n">
-        <v>694263000</v>
+        <v>772679000</v>
       </c>
       <c r="AY4" t="n">
-        <v>2171626000</v>
+        <v>2628029000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2171626000</v>
+        <v>2628029000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>5798958</v>
+        <v>-13152683.139854</v>
       </c>
       <c r="C5" t="n">
-        <v>0.246</v>
+        <v>0.3864</v>
       </c>
       <c r="D5" t="n">
-        <v>1309642000</v>
+        <v>1034149000</v>
       </c>
       <c r="E5" t="n">
-        <v>23573000</v>
+        <v>-34039000</v>
       </c>
       <c r="F5" t="n">
-        <v>23573000</v>
+        <v>-34039000</v>
       </c>
       <c r="G5" t="n">
-        <v>720033000</v>
+        <v>373134000</v>
       </c>
       <c r="H5" t="n">
-        <v>146734000</v>
+        <v>173179000</v>
       </c>
       <c r="I5" t="n">
-        <v>786064000</v>
+        <v>694828000</v>
       </c>
       <c r="J5" t="n">
-        <v>1333215000</v>
+        <v>1000110000</v>
       </c>
       <c r="K5" t="n">
-        <v>1186481000</v>
+        <v>826931000</v>
       </c>
       <c r="L5" t="n">
-        <v>7623000</v>
+        <v>5389000</v>
       </c>
       <c r="M5" t="n">
-        <v>7246000</v>
+        <v>16422000</v>
       </c>
       <c r="N5" t="n">
-        <v>14869000</v>
+        <v>21811000</v>
       </c>
       <c r="O5" t="n">
-        <v>702258958</v>
+        <v>394020316.860146</v>
       </c>
       <c r="P5" t="n">
-        <v>720033000</v>
+        <v>373134000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1193681000</v>
+        <v>1212364000</v>
       </c>
       <c r="R5" t="n">
-        <v>1094478000</v>
+        <v>709887000</v>
       </c>
       <c r="S5" t="n">
-        <v>2278585161</v>
+        <v>2271063422</v>
       </c>
       <c r="T5" t="n">
-        <v>2278490319</v>
+        <v>2271063422</v>
       </c>
       <c r="U5" t="n">
-        <v>0.316</v>
+        <v>0.164</v>
       </c>
       <c r="V5" t="n">
-        <v>0.316</v>
+        <v>0.164</v>
       </c>
       <c r="W5" t="n">
-        <v>720033000</v>
+        <v>373134000</v>
       </c>
       <c r="X5" t="n">
-        <v>720033000</v>
+        <v>373134000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>720033000</v>
+        <v>373134000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-169611000</v>
+        <v>-124194000</v>
       </c>
       <c r="AB5" t="n">
-        <v>889644000</v>
+        <v>497328000</v>
       </c>
       <c r="AC5" t="n">
-        <v>889644000</v>
+        <v>497328000</v>
       </c>
       <c r="AD5" t="n">
-        <v>289591000</v>
+        <v>313181000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1179235000</v>
+        <v>810509000</v>
       </c>
       <c r="AF5" t="n">
-        <v>30722000</v>
+        <v>-8123000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-4393000</v>
+        <v>-78792000</v>
       </c>
       <c r="AH5" t="n">
-        <v>572000</v>
+        <v>-48986000</v>
       </c>
       <c r="AI5" t="n">
-        <v>3821000</v>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
+        <v>23585000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>104193000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>7623000</v>
+        <v>5389000</v>
       </c>
       <c r="AM5" t="n">
-        <v>7246000</v>
+        <v>16422000</v>
       </c>
       <c r="AN5" t="n">
-        <v>14869000</v>
+        <v>21811000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1132167000</v>
+        <v>865120000</v>
       </c>
       <c r="AP5" t="n">
-        <v>407617000</v>
+        <v>517536000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>53122000</v>
+        <v>51111000</v>
       </c>
       <c r="AR5" t="n">
-        <v>146734000</v>
+        <v>173179000</v>
       </c>
       <c r="AS5" t="n">
-        <v>146734000</v>
+        <v>173179000</v>
       </c>
       <c r="AT5" t="n">
-        <v>241629000</v>
+        <v>285973000</v>
       </c>
       <c r="AU5" t="n">
-        <v>43986000</v>
+        <v>41597000</v>
       </c>
       <c r="AV5" t="n">
-        <v>197643000</v>
+        <v>244376000</v>
       </c>
       <c r="AW5" t="n">
-        <v>1539784000</v>
+        <v>1382656000</v>
       </c>
       <c r="AX5" t="n">
-        <v>786064000</v>
+        <v>694828000</v>
       </c>
       <c r="AY5" t="n">
-        <v>2325848000</v>
+        <v>2077484000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2325848000</v>
+        <v>2077484000</v>
       </c>
     </row>
   </sheetData>
@@ -1683,276 +1683,272 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>48800000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>2271063422</v>
+        <v>2320366422</v>
       </c>
       <c r="D2" t="n">
-        <v>2319863422</v>
+        <v>2320366422</v>
       </c>
       <c r="E2" t="n">
-        <v>161762000</v>
+        <v>88600000</v>
       </c>
       <c r="F2" t="n">
-        <v>4197776000</v>
+        <v>3728445000</v>
       </c>
       <c r="G2" t="n">
-        <v>5591620000</v>
+        <v>5070624000</v>
       </c>
       <c r="H2" t="n">
-        <v>2393564000</v>
+        <v>1954767000</v>
       </c>
       <c r="I2" t="n">
-        <v>4197776000</v>
+        <v>3728445000</v>
       </c>
       <c r="J2" t="n">
-        <v>131296000</v>
+        <v>61416000</v>
       </c>
       <c r="K2" t="n">
-        <v>5561154000</v>
+        <v>5043440000</v>
       </c>
       <c r="L2" t="n">
-        <v>5561154000</v>
+        <v>5043440000</v>
       </c>
       <c r="M2" t="n">
-        <v>6155828000</v>
+        <v>5672320000</v>
       </c>
       <c r="N2" t="n">
-        <v>594674000</v>
+        <v>628880000</v>
       </c>
       <c r="O2" t="n">
-        <v>5561154000</v>
+        <v>5043440000</v>
       </c>
       <c r="P2" t="n">
-        <v>231883000</v>
+        <v>259669000</v>
       </c>
       <c r="Q2" t="n">
-        <v>5443670000</v>
+        <v>3730920000</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1258234000</v>
       </c>
       <c r="S2" t="n">
-        <v>142148000</v>
+        <v>142179000</v>
       </c>
       <c r="T2" t="n">
-        <v>142148000</v>
+        <v>142179000</v>
       </c>
       <c r="U2" t="n">
-        <v>2025369000</v>
+        <v>1733130000</v>
       </c>
       <c r="V2" t="n">
-        <v>861949000</v>
+        <v>651943000</v>
       </c>
       <c r="W2" t="n">
-        <v>40337000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>44964000</v>
-      </c>
+        <v>36713000</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>514208000</v>
+        <v>434022000</v>
       </c>
       <c r="Z2" t="n">
-        <v>150896000</v>
+        <v>137068000</v>
       </c>
       <c r="AA2" t="n">
-        <v>111544000</v>
+        <v>44140000</v>
       </c>
       <c r="AB2" t="n">
-        <v>111544000</v>
+        <v>44140000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1163420000</v>
+        <v>1081187000</v>
       </c>
       <c r="AD2" t="n">
-        <v>50218000</v>
+        <v>44460000</v>
       </c>
       <c r="AE2" t="n">
-        <v>19752000</v>
+        <v>17276000</v>
       </c>
       <c r="AF2" t="n">
-        <v>30466000</v>
+        <v>27184000</v>
       </c>
       <c r="AG2" t="n">
-        <v>946217000</v>
+        <v>879590000</v>
       </c>
       <c r="AH2" t="n">
-        <v>304254000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>110124000</v>
-      </c>
+        <v>394958000</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>212079000</v>
+        <v>202880000</v>
       </c>
       <c r="AK2" t="n">
-        <v>319760000</v>
+        <v>281752000</v>
       </c>
       <c r="AL2" t="n">
-        <v>8181197000</v>
+        <v>7405450000</v>
       </c>
       <c r="AM2" t="n">
-        <v>4624213000</v>
+        <v>4369496000</v>
       </c>
       <c r="AN2" t="n">
-        <v>8930000</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
+        <v>5000000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>27454000</v>
+      </c>
       <c r="AP2" t="n">
-        <v>120956000</v>
+        <v>76630000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>207633000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>207633000</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+        <v>38110000</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>38110000</v>
+      </c>
       <c r="AT2" t="n">
-        <v>57348000</v>
+        <v>195999000</v>
       </c>
       <c r="AU2" t="n">
-        <v>54413000</v>
+        <v>190249000</v>
       </c>
       <c r="AV2" t="n">
-        <v>2935000</v>
+        <v>5750000</v>
       </c>
       <c r="AW2" t="n">
         <v>6509000</v>
       </c>
       <c r="AX2" t="n">
-        <v>1363378000</v>
+        <v>1314995000</v>
       </c>
       <c r="AY2" t="n">
-        <v>257302000</v>
+        <v>266335000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1106076000</v>
+        <v>1048660000</v>
       </c>
       <c r="BA2" t="n">
-        <v>2763064000</v>
+        <v>2635420000</v>
       </c>
       <c r="BB2" t="n">
-        <v>-1048773000</v>
+        <v>-685335000</v>
       </c>
       <c r="BC2" t="n">
-        <v>3811837000</v>
+        <v>3320755000</v>
       </c>
       <c r="BD2" t="n">
-        <v>653328000</v>
-      </c>
-      <c r="BE2" t="inlineStr"/>
+        <v>558084000</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>419611000</v>
+      </c>
       <c r="BF2" t="n">
-        <v>626394000</v>
+        <v>531226000</v>
       </c>
       <c r="BG2" t="n">
-        <v>799756000</v>
+        <v>655533000</v>
       </c>
       <c r="BH2" t="n">
-        <v>1732359000</v>
+        <v>1575912000</v>
       </c>
       <c r="BI2" t="n">
         <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>3556984000</v>
+        <v>3035954000</v>
       </c>
       <c r="BK2" t="n">
-        <v>12103000</v>
+        <v>24557000</v>
       </c>
       <c r="BL2" t="n">
-        <v>576326000</v>
+        <v>544487000</v>
       </c>
       <c r="BM2" t="n">
-        <v>39328000</v>
+        <v>51847000</v>
       </c>
       <c r="BN2" t="n">
-        <v>536998000</v>
+        <v>492640000</v>
       </c>
       <c r="BO2" t="n">
-        <v>36163000</v>
+        <v>31310000</v>
       </c>
       <c r="BP2" t="n">
-        <v>98215000</v>
+        <v>108344000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-27002000</v>
+        <v>-3821000</v>
       </c>
       <c r="BR2" t="n">
-        <v>125217000</v>
+        <v>112165000</v>
       </c>
       <c r="BS2" t="n">
-        <v>2834177000</v>
+        <v>2327256000</v>
       </c>
       <c r="BT2" t="n">
-        <v>777551000</v>
+        <v>1251650000</v>
       </c>
       <c r="BU2" t="n">
-        <v>2056626000</v>
+        <v>1075606000</v>
       </c>
       <c r="BV2" t="n">
-        <v>2056626000</v>
+        <v>1075606000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
-      </c>
-      <c r="B3" t="n">
-        <v>48800000</v>
-      </c>
+        <v>44926</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2271063422</v>
+        <v>2319863422</v>
       </c>
       <c r="D3" t="n">
         <v>2319863422</v>
       </c>
       <c r="E3" t="n">
-        <v>281809000</v>
+        <v>97661000</v>
       </c>
       <c r="F3" t="n">
-        <v>4481232000</v>
+        <v>4110901000</v>
       </c>
       <c r="G3" t="n">
-        <v>6149493000</v>
+        <v>5508716000</v>
       </c>
       <c r="H3" t="n">
-        <v>2775375000</v>
+        <v>2422561000</v>
       </c>
       <c r="I3" t="n">
-        <v>4481232000</v>
+        <v>4110901000</v>
       </c>
       <c r="J3" t="n">
-        <v>52371000</v>
+        <v>64703000</v>
       </c>
       <c r="K3" t="n">
-        <v>5920055000</v>
+        <v>5475758000</v>
       </c>
       <c r="L3" t="n">
-        <v>5920055000</v>
+        <v>5475758000</v>
       </c>
       <c r="M3" t="n">
-        <v>6573864000</v>
+        <v>6114004000</v>
       </c>
       <c r="N3" t="n">
-        <v>653809000</v>
+        <v>638246000</v>
       </c>
       <c r="O3" t="n">
-        <v>5920055000</v>
+        <v>5475758000</v>
       </c>
       <c r="P3" t="n">
-        <v>247361000</v>
+        <v>254829000</v>
       </c>
       <c r="Q3" t="n">
-        <v>5148604000</v>
+        <v>4376657000</v>
       </c>
       <c r="R3" t="n">
-        <v>671154000</v>
+        <v>1026187000</v>
       </c>
       <c r="S3" t="n">
         <v>142148000</v>
@@ -1961,216 +1957,218 @@
         <v>142148000</v>
       </c>
       <c r="U3" t="n">
-        <v>2093923000</v>
+        <v>1701887000</v>
       </c>
       <c r="V3" t="n">
-        <v>835737000</v>
+        <v>667766000</v>
       </c>
       <c r="W3" t="n">
-        <v>50840000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>45111000</v>
-      </c>
+        <v>37850000</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>494434000</v>
+        <v>456237000</v>
       </c>
       <c r="Z3" t="n">
-        <v>216137000</v>
+        <v>134215000</v>
       </c>
       <c r="AA3" t="n">
-        <v>29215000</v>
+        <v>39464000</v>
       </c>
       <c r="AB3" t="n">
-        <v>29215000</v>
+        <v>39464000</v>
       </c>
       <c r="AC3" t="n">
-        <v>1258186000</v>
+        <v>1034121000</v>
       </c>
       <c r="AD3" t="n">
-        <v>252594000</v>
+        <v>58197000</v>
       </c>
       <c r="AE3" t="n">
-        <v>23156000</v>
+        <v>25239000</v>
       </c>
       <c r="AF3" t="n">
-        <v>229438000</v>
+        <v>32958000</v>
       </c>
       <c r="AG3" t="n">
-        <v>834100000</v>
+        <v>802126000</v>
       </c>
       <c r="AH3" t="n">
-        <v>285828000</v>
+        <v>313636000</v>
       </c>
       <c r="AI3" t="n">
-        <v>36000000</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>205440000</v>
+        <v>179938000</v>
       </c>
       <c r="AK3" t="n">
-        <v>306832000</v>
+        <v>308552000</v>
       </c>
       <c r="AL3" t="n">
-        <v>8667787000</v>
+        <v>7815891000</v>
       </c>
       <c r="AM3" t="n">
-        <v>4634226000</v>
+        <v>4359209000</v>
       </c>
       <c r="AN3" t="n">
         <v>5000000</v>
       </c>
-      <c r="AO3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>29117000</v>
+      </c>
       <c r="AP3" t="n">
-        <v>92871000</v>
+        <v>81290000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>200000000</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>200000000</v>
-      </c>
+        <v>38110000</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>38110000</v>
       </c>
       <c r="AT3" t="n">
-        <v>45184000</v>
+        <v>133710000</v>
       </c>
       <c r="AU3" t="n">
-        <v>42184000</v>
+        <v>132960000</v>
       </c>
       <c r="AV3" t="n">
-        <v>3000000</v>
+        <v>750000</v>
       </c>
       <c r="AW3" t="n">
         <v>6509000</v>
       </c>
       <c r="AX3" t="n">
-        <v>1438823000</v>
+        <v>1364857000</v>
       </c>
       <c r="AY3" t="n">
-        <v>309774000</v>
+        <v>273614000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1129049000</v>
+        <v>1091243000</v>
       </c>
       <c r="BA3" t="n">
-        <v>2756415000</v>
+        <v>2648339000</v>
       </c>
       <c r="BB3" t="n">
-        <v>-901326000</v>
+        <v>-792609000</v>
       </c>
       <c r="BC3" t="n">
-        <v>3657741000</v>
+        <v>3440948000</v>
       </c>
       <c r="BD3" t="n">
-        <v>617542000</v>
-      </c>
-      <c r="BE3" t="inlineStr"/>
+        <v>592072000</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>477176000</v>
+      </c>
       <c r="BF3" t="n">
-        <v>611182000</v>
+        <v>596114000</v>
       </c>
       <c r="BG3" t="n">
-        <v>697356000</v>
+        <v>677610000</v>
       </c>
       <c r="BH3" t="n">
-        <v>1731661000</v>
+        <v>1575152000</v>
       </c>
       <c r="BI3" t="n">
         <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>4033561000</v>
+        <v>3456682000</v>
       </c>
       <c r="BK3" t="n">
-        <v>24473000</v>
+        <v>17710000</v>
       </c>
       <c r="BL3" t="n">
-        <v>557991000</v>
+        <v>558958000</v>
       </c>
       <c r="BM3" t="n">
-        <v>52339000</v>
+        <v>51915000</v>
       </c>
       <c r="BN3" t="n">
-        <v>505652000</v>
+        <v>507043000</v>
       </c>
       <c r="BO3" t="n">
-        <v>72270000</v>
+        <v>278556000</v>
       </c>
       <c r="BP3" t="n">
-        <v>139113000</v>
+        <v>137875000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-5018000</v>
+        <v>-5059000</v>
       </c>
       <c r="BR3" t="n">
-        <v>144131000</v>
+        <v>142934000</v>
       </c>
       <c r="BS3" t="n">
-        <v>3239714000</v>
+        <v>2463583000</v>
       </c>
       <c r="BT3" t="n">
-        <v>944247000</v>
+        <v>521350000</v>
       </c>
       <c r="BU3" t="n">
-        <v>2295467000</v>
+        <v>1942233000</v>
       </c>
       <c r="BV3" t="n">
-        <v>2295467000</v>
+        <v>1942233000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
+        <v>45291</v>
+      </c>
+      <c r="B4" t="n">
+        <v>48800000</v>
+      </c>
       <c r="C4" t="n">
-        <v>2319863422</v>
+        <v>2271063422</v>
       </c>
       <c r="D4" t="n">
         <v>2319863422</v>
       </c>
       <c r="E4" t="n">
-        <v>97661000</v>
+        <v>281809000</v>
       </c>
       <c r="F4" t="n">
-        <v>4110901000</v>
+        <v>4481232000</v>
       </c>
       <c r="G4" t="n">
-        <v>5508716000</v>
+        <v>6149493000</v>
       </c>
       <c r="H4" t="n">
-        <v>2422561000</v>
+        <v>2775375000</v>
       </c>
       <c r="I4" t="n">
-        <v>4110901000</v>
+        <v>4481232000</v>
       </c>
       <c r="J4" t="n">
-        <v>64703000</v>
+        <v>52371000</v>
       </c>
       <c r="K4" t="n">
-        <v>5475758000</v>
+        <v>5920055000</v>
       </c>
       <c r="L4" t="n">
-        <v>5475758000</v>
+        <v>5920055000</v>
       </c>
       <c r="M4" t="n">
-        <v>6114004000</v>
+        <v>6573864000</v>
       </c>
       <c r="N4" t="n">
-        <v>638246000</v>
+        <v>653809000</v>
       </c>
       <c r="O4" t="n">
-        <v>5475758000</v>
+        <v>5920055000</v>
       </c>
       <c r="P4" t="n">
-        <v>254829000</v>
+        <v>247361000</v>
       </c>
       <c r="Q4" t="n">
-        <v>4376657000</v>
+        <v>5148604000</v>
       </c>
       <c r="R4" t="n">
-        <v>1026187000</v>
+        <v>671154000</v>
       </c>
       <c r="S4" t="n">
         <v>142148000</v>
@@ -2179,378 +2177,380 @@
         <v>142148000</v>
       </c>
       <c r="U4" t="n">
-        <v>1701887000</v>
+        <v>2093923000</v>
       </c>
       <c r="V4" t="n">
-        <v>667766000</v>
+        <v>835737000</v>
       </c>
       <c r="W4" t="n">
-        <v>37850000</v>
-      </c>
-      <c r="X4" t="inlineStr"/>
+        <v>50840000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>45111000</v>
+      </c>
       <c r="Y4" t="n">
-        <v>456237000</v>
+        <v>494434000</v>
       </c>
       <c r="Z4" t="n">
-        <v>134215000</v>
+        <v>216137000</v>
       </c>
       <c r="AA4" t="n">
-        <v>39464000</v>
+        <v>29215000</v>
       </c>
       <c r="AB4" t="n">
-        <v>39464000</v>
+        <v>29215000</v>
       </c>
       <c r="AC4" t="n">
-        <v>1034121000</v>
+        <v>1258186000</v>
       </c>
       <c r="AD4" t="n">
-        <v>58197000</v>
+        <v>252594000</v>
       </c>
       <c r="AE4" t="n">
-        <v>25239000</v>
+        <v>23156000</v>
       </c>
       <c r="AF4" t="n">
-        <v>32958000</v>
+        <v>229438000</v>
       </c>
       <c r="AG4" t="n">
-        <v>802126000</v>
+        <v>834100000</v>
       </c>
       <c r="AH4" t="n">
-        <v>313636000</v>
+        <v>285828000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>36000000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>179938000</v>
+        <v>205440000</v>
       </c>
       <c r="AK4" t="n">
-        <v>308552000</v>
+        <v>306832000</v>
       </c>
       <c r="AL4" t="n">
-        <v>7815891000</v>
+        <v>8667787000</v>
       </c>
       <c r="AM4" t="n">
-        <v>4359209000</v>
+        <v>4634226000</v>
       </c>
       <c r="AN4" t="n">
         <v>5000000</v>
       </c>
-      <c r="AO4" t="n">
-        <v>29117000</v>
-      </c>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>81290000</v>
+        <v>92871000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>38110000</v>
-      </c>
-      <c r="AR4" t="inlineStr"/>
+        <v>200000000</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>200000000</v>
+      </c>
       <c r="AS4" t="n">
-        <v>38110000</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>133710000</v>
+        <v>45184000</v>
       </c>
       <c r="AU4" t="n">
-        <v>132960000</v>
+        <v>42184000</v>
       </c>
       <c r="AV4" t="n">
-        <v>750000</v>
+        <v>3000000</v>
       </c>
       <c r="AW4" t="n">
         <v>6509000</v>
       </c>
       <c r="AX4" t="n">
-        <v>1364857000</v>
+        <v>1438823000</v>
       </c>
       <c r="AY4" t="n">
-        <v>273614000</v>
+        <v>309774000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1091243000</v>
+        <v>1129049000</v>
       </c>
       <c r="BA4" t="n">
-        <v>2648339000</v>
+        <v>2756415000</v>
       </c>
       <c r="BB4" t="n">
-        <v>-792609000</v>
+        <v>-901326000</v>
       </c>
       <c r="BC4" t="n">
-        <v>3440948000</v>
+        <v>3657741000</v>
       </c>
       <c r="BD4" t="n">
-        <v>592072000</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>477176000</v>
-      </c>
+        <v>617542000</v>
+      </c>
+      <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="n">
-        <v>596114000</v>
+        <v>611182000</v>
       </c>
       <c r="BG4" t="n">
-        <v>677610000</v>
+        <v>697356000</v>
       </c>
       <c r="BH4" t="n">
-        <v>1575152000</v>
+        <v>1731661000</v>
       </c>
       <c r="BI4" t="n">
         <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>3456682000</v>
+        <v>4033561000</v>
       </c>
       <c r="BK4" t="n">
-        <v>17710000</v>
+        <v>24473000</v>
       </c>
       <c r="BL4" t="n">
-        <v>558958000</v>
+        <v>557991000</v>
       </c>
       <c r="BM4" t="n">
-        <v>51915000</v>
+        <v>52339000</v>
       </c>
       <c r="BN4" t="n">
-        <v>507043000</v>
+        <v>505652000</v>
       </c>
       <c r="BO4" t="n">
-        <v>278556000</v>
+        <v>72270000</v>
       </c>
       <c r="BP4" t="n">
-        <v>137875000</v>
+        <v>139113000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-5059000</v>
+        <v>-5018000</v>
       </c>
       <c r="BR4" t="n">
-        <v>142934000</v>
+        <v>144131000</v>
       </c>
       <c r="BS4" t="n">
-        <v>2463583000</v>
+        <v>3239714000</v>
       </c>
       <c r="BT4" t="n">
-        <v>521350000</v>
+        <v>944247000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1942233000</v>
+        <v>2295467000</v>
       </c>
       <c r="BV4" t="n">
-        <v>1942233000</v>
+        <v>2295467000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
+        <v>45657</v>
+      </c>
+      <c r="B5" t="n">
+        <v>48800000</v>
+      </c>
       <c r="C5" t="n">
-        <v>2320366422</v>
+        <v>2271063422</v>
       </c>
       <c r="D5" t="n">
-        <v>2320366422</v>
+        <v>2319863422</v>
       </c>
       <c r="E5" t="n">
-        <v>88600000</v>
+        <v>161762000</v>
       </c>
       <c r="F5" t="n">
-        <v>3728445000</v>
+        <v>4197776000</v>
       </c>
       <c r="G5" t="n">
-        <v>5070624000</v>
+        <v>5591620000</v>
       </c>
       <c r="H5" t="n">
-        <v>1954767000</v>
+        <v>2393564000</v>
       </c>
       <c r="I5" t="n">
-        <v>3728445000</v>
+        <v>4197776000</v>
       </c>
       <c r="J5" t="n">
-        <v>61416000</v>
+        <v>131296000</v>
       </c>
       <c r="K5" t="n">
-        <v>5043440000</v>
+        <v>5561154000</v>
       </c>
       <c r="L5" t="n">
-        <v>5043440000</v>
+        <v>5561154000</v>
       </c>
       <c r="M5" t="n">
-        <v>5672320000</v>
+        <v>6155828000</v>
       </c>
       <c r="N5" t="n">
-        <v>628880000</v>
+        <v>594674000</v>
       </c>
       <c r="O5" t="n">
-        <v>5043440000</v>
+        <v>5561154000</v>
       </c>
       <c r="P5" t="n">
-        <v>259669000</v>
+        <v>231883000</v>
       </c>
       <c r="Q5" t="n">
-        <v>3730920000</v>
+        <v>5443670000</v>
       </c>
       <c r="R5" t="n">
-        <v>1258234000</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>142179000</v>
+        <v>142148000</v>
       </c>
       <c r="T5" t="n">
-        <v>142179000</v>
+        <v>142148000</v>
       </c>
       <c r="U5" t="n">
-        <v>1733130000</v>
+        <v>2025369000</v>
       </c>
       <c r="V5" t="n">
-        <v>651943000</v>
+        <v>861949000</v>
       </c>
       <c r="W5" t="n">
-        <v>36713000</v>
-      </c>
-      <c r="X5" t="inlineStr"/>
+        <v>40337000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>44964000</v>
+      </c>
       <c r="Y5" t="n">
-        <v>434022000</v>
+        <v>514208000</v>
       </c>
       <c r="Z5" t="n">
-        <v>137068000</v>
+        <v>150896000</v>
       </c>
       <c r="AA5" t="n">
-        <v>44140000</v>
+        <v>111544000</v>
       </c>
       <c r="AB5" t="n">
-        <v>44140000</v>
+        <v>111544000</v>
       </c>
       <c r="AC5" t="n">
-        <v>1081187000</v>
+        <v>1163420000</v>
       </c>
       <c r="AD5" t="n">
-        <v>44460000</v>
+        <v>50218000</v>
       </c>
       <c r="AE5" t="n">
-        <v>17276000</v>
+        <v>19752000</v>
       </c>
       <c r="AF5" t="n">
-        <v>27184000</v>
+        <v>30466000</v>
       </c>
       <c r="AG5" t="n">
-        <v>879590000</v>
+        <v>946217000</v>
       </c>
       <c r="AH5" t="n">
-        <v>394958000</v>
-      </c>
-      <c r="AI5" t="inlineStr"/>
+        <v>304254000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>110124000</v>
+      </c>
       <c r="AJ5" t="n">
-        <v>202880000</v>
+        <v>212079000</v>
       </c>
       <c r="AK5" t="n">
-        <v>281752000</v>
+        <v>319760000</v>
       </c>
       <c r="AL5" t="n">
-        <v>7405450000</v>
+        <v>8181197000</v>
       </c>
       <c r="AM5" t="n">
-        <v>4369496000</v>
+        <v>4624213000</v>
       </c>
       <c r="AN5" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>27454000</v>
-      </c>
+        <v>8930000</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>76630000</v>
+        <v>120956000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>38110000</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="n">
-        <v>38110000</v>
-      </c>
+        <v>207633000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>207633000</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>195999000</v>
+        <v>57348000</v>
       </c>
       <c r="AU5" t="n">
-        <v>190249000</v>
+        <v>54413000</v>
       </c>
       <c r="AV5" t="n">
-        <v>5750000</v>
+        <v>2935000</v>
       </c>
       <c r="AW5" t="n">
         <v>6509000</v>
       </c>
       <c r="AX5" t="n">
-        <v>1314995000</v>
+        <v>1363378000</v>
       </c>
       <c r="AY5" t="n">
-        <v>266335000</v>
+        <v>257302000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1048660000</v>
+        <v>1106076000</v>
       </c>
       <c r="BA5" t="n">
-        <v>2635420000</v>
+        <v>2763064000</v>
       </c>
       <c r="BB5" t="n">
-        <v>-685335000</v>
+        <v>-1048773000</v>
       </c>
       <c r="BC5" t="n">
-        <v>3320755000</v>
+        <v>3811837000</v>
       </c>
       <c r="BD5" t="n">
-        <v>558084000</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>419611000</v>
-      </c>
+        <v>653328000</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="n">
-        <v>531226000</v>
+        <v>626394000</v>
       </c>
       <c r="BG5" t="n">
-        <v>655533000</v>
+        <v>799756000</v>
       </c>
       <c r="BH5" t="n">
-        <v>1575912000</v>
+        <v>1732359000</v>
       </c>
       <c r="BI5" t="n">
         <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>3035954000</v>
+        <v>3556984000</v>
       </c>
       <c r="BK5" t="n">
-        <v>24557000</v>
+        <v>12103000</v>
       </c>
       <c r="BL5" t="n">
-        <v>544487000</v>
+        <v>576326000</v>
       </c>
       <c r="BM5" t="n">
-        <v>51847000</v>
+        <v>39328000</v>
       </c>
       <c r="BN5" t="n">
-        <v>492640000</v>
+        <v>536998000</v>
       </c>
       <c r="BO5" t="n">
-        <v>31310000</v>
+        <v>36163000</v>
       </c>
       <c r="BP5" t="n">
-        <v>108344000</v>
+        <v>98215000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-3821000</v>
+        <v>-27002000</v>
       </c>
       <c r="BR5" t="n">
-        <v>112165000</v>
+        <v>125217000</v>
       </c>
       <c r="BS5" t="n">
-        <v>2327256000</v>
+        <v>2834177000</v>
       </c>
       <c r="BT5" t="n">
-        <v>1251650000</v>
+        <v>777551000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1075606000</v>
+        <v>2056626000</v>
       </c>
       <c r="BV5" t="n">
-        <v>1075606000</v>
+        <v>2056626000</v>
       </c>
     </row>
   </sheetData>
@@ -2841,634 +2841,634 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>629393000</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>816767000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-71958000</v>
+      </c>
       <c r="D2" t="n">
-        <v>-200000000</v>
+        <v>-111160000</v>
       </c>
       <c r="E2" t="n">
-        <v>622000</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>5200000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41830000</v>
+      </c>
       <c r="G2" t="n">
-        <v>-79139000</v>
+        <v>-175602000</v>
       </c>
       <c r="H2" t="n">
-        <v>2056626000</v>
+        <v>1075606000</v>
       </c>
       <c r="I2" t="n">
-        <v>2295467000</v>
+        <v>1234022000</v>
       </c>
       <c r="J2" t="n">
-        <v>-238841000</v>
+        <v>-158416000</v>
       </c>
       <c r="K2" t="n">
-        <v>-1078214000</v>
+        <v>-502485000</v>
       </c>
       <c r="L2" t="n">
-        <v>4746000</v>
+        <v>3490000</v>
       </c>
       <c r="M2" t="n">
-        <v>-11548000</v>
+        <v>-3220000</v>
       </c>
       <c r="N2" t="n">
-        <v>-720353000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-720353000</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+        <v>-214346000</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>-30128000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-71958000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>41830000</v>
+      </c>
       <c r="S2" t="n">
-        <v>-199378000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-199378000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-200000000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>622000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
+        <v>-105960000</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>-105960000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-111160000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>5200000</v>
+      </c>
       <c r="Z2" t="n">
-        <v>130841000</v>
+        <v>-648300000</v>
       </c>
       <c r="AA2" t="n">
-        <v>44078000</v>
+        <v>27131000</v>
       </c>
       <c r="AB2" t="n">
-        <v>15187000</v>
+        <v>17063000</v>
       </c>
       <c r="AC2" t="n">
-        <v>169296000</v>
+        <v>-268723000</v>
       </c>
       <c r="AD2" t="n">
-        <v>547746000</v>
+        <v>927575000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-378450000</v>
+        <v>-1196298000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-19685000</v>
+        <v>-256385000</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-19685000</v>
+        <v>-256385000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1202000</v>
+        <v>-49399000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-1202000</v>
+        <v>-49399000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-76833000</v>
+        <v>-124937000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1104000</v>
+        <v>1266000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-77937000</v>
+        <v>-126203000</v>
       </c>
       <c r="AN2" t="n">
-        <v>708532000</v>
+        <v>992369000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-399869000</v>
+        <v>-271278000</v>
       </c>
       <c r="AP2" t="n">
-        <v>23237000</v>
+        <v>-42703000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-31464000</v>
+        <v>17870000</v>
       </c>
       <c r="AR2" t="n">
-        <v>5131000</v>
+        <v>13238000</v>
       </c>
       <c r="AS2" t="n">
-        <v>-3800000</v>
+        <v>-8070000</v>
       </c>
       <c r="AT2" t="n">
-        <v>53370000</v>
+        <v>-65741000</v>
       </c>
       <c r="AU2" t="n">
-        <v>-5389000</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
+        <v>-7623000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
       <c r="AW2" t="n">
-        <v>173179000</v>
+        <v>146734000</v>
       </c>
       <c r="AX2" t="n">
-        <v>21729000</v>
+        <v>9318000</v>
       </c>
       <c r="AY2" t="n">
-        <v>151450000</v>
+        <v>137416000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-44753000</v>
+        <v>-27966000</v>
       </c>
       <c r="BA2" t="n">
-        <v>-5609000</v>
+        <v>572000</v>
       </c>
       <c r="BB2" t="n">
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>810509000</v>
+        <v>1179235000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>1058248000</v>
+        <v>767865000</v>
       </c>
       <c r="C3" t="n">
+        <v>-1919000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-4410000</v>
+      </c>
+      <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" t="n">
-        <v>-84410000</v>
-      </c>
-      <c r="E3" t="n">
-        <v>200878000</v>
-      </c>
       <c r="F3" t="n">
-        <v>7468000</v>
+        <v>4840000</v>
       </c>
       <c r="G3" t="n">
-        <v>-44630000</v>
+        <v>-85068000</v>
       </c>
       <c r="H3" t="n">
-        <v>2295467000</v>
+        <v>1942233000</v>
       </c>
       <c r="I3" t="n">
-        <v>1942233000</v>
+        <v>1075606000</v>
       </c>
       <c r="J3" t="n">
-        <v>353234000</v>
+        <v>866627000</v>
       </c>
       <c r="K3" t="n">
-        <v>-387518000</v>
+        <v>-399541000</v>
       </c>
       <c r="L3" t="n">
-        <v>-1137000</v>
+        <v>-40664000</v>
       </c>
       <c r="M3" t="n">
-        <v>-849000</v>
+        <v>-1065000</v>
       </c>
       <c r="N3" t="n">
-        <v>-347565000</v>
+        <v>-230159000</v>
       </c>
       <c r="O3" t="n">
-        <v>-347565000</v>
+        <v>-230159000</v>
       </c>
       <c r="P3" t="n">
-        <v>7468000</v>
+        <v>2921000</v>
       </c>
       <c r="Q3" t="n">
+        <v>-1919000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>4840000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-4410000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-4410000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-4410000</v>
+      </c>
+      <c r="V3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="n">
-        <v>7468000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>116468000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>116468000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-84410000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>200878000</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
       <c r="Z3" t="n">
-        <v>-362126000</v>
+        <v>413235000</v>
       </c>
       <c r="AA3" t="n">
-        <v>40268000</v>
+        <v>31409000</v>
       </c>
       <c r="AB3" t="n">
-        <v>14475000</v>
+        <v>13873000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-616249000</v>
+        <v>429465000</v>
       </c>
       <c r="AD3" t="n">
-        <v>405497000</v>
+        <v>835577000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-1021746000</v>
+        <v>-406112000</v>
       </c>
       <c r="AF3" t="n">
-        <v>184921000</v>
+        <v>77740000</v>
       </c>
       <c r="AG3" t="n">
-        <v>262340000</v>
+        <v>159882000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-77419000</v>
+        <v>-82142000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-13678000</v>
+        <v>-15536000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-13678000</v>
+        <v>-15536000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-16046000</v>
+        <v>-65676000</v>
       </c>
       <c r="AL3" t="n">
-        <v>14906000</v>
+        <v>3856000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-30952000</v>
+        <v>-69532000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1102878000</v>
+        <v>852933000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-359795000</v>
+        <v>-313635000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-96014000</v>
+        <v>-41751000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-87969000</v>
+        <v>28932000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-17351000</v>
+        <v>-39875000</v>
       </c>
       <c r="AS3" t="n">
-        <v>7154000</v>
+        <v>-1663000</v>
       </c>
       <c r="AT3" t="n">
-        <v>2152000</v>
+        <v>-29145000</v>
       </c>
       <c r="AU3" t="n">
-        <v>-9949000</v>
+        <v>-8715000</v>
       </c>
       <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="n">
-        <v>166609000</v>
+        <v>155953000</v>
       </c>
       <c r="AX3" t="n">
-        <v>18730000</v>
+        <v>15299000</v>
       </c>
       <c r="AY3" t="n">
-        <v>147879000</v>
+        <v>140654000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-39667000</v>
+        <v>-30574000</v>
       </c>
       <c r="BA3" t="n">
-        <v>-8648000</v>
+        <v>47000</v>
       </c>
       <c r="BB3" t="n">
-        <v>393000</v>
+        <v>-9242000</v>
       </c>
       <c r="BC3" t="n">
-        <v>1431554000</v>
+        <v>1092205000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>767865000</v>
+        <v>1058248000</v>
       </c>
       <c r="C4" t="n">
-        <v>-1919000</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-4410000</v>
+        <v>-84410000</v>
       </c>
       <c r="E4" t="n">
+        <v>200878000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>7468000</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-44630000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2295467000</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1942233000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>353234000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-387518000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-1137000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-849000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-347565000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-347565000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>7468000</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="n">
-        <v>4840000</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-85068000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1942233000</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1075606000</v>
-      </c>
-      <c r="J4" t="n">
-        <v>866627000</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-399541000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-40664000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>-1065000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-230159000</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-230159000</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2921000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-1919000</v>
-      </c>
       <c r="R4" t="n">
-        <v>4840000</v>
+        <v>7468000</v>
       </c>
       <c r="S4" t="n">
-        <v>-4410000</v>
+        <v>116468000</v>
       </c>
       <c r="T4" t="n">
-        <v>-4410000</v>
+        <v>116468000</v>
       </c>
       <c r="U4" t="n">
-        <v>-4410000</v>
+        <v>-84410000</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
+        <v>200878000</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>413235000</v>
+        <v>-362126000</v>
       </c>
       <c r="AA4" t="n">
-        <v>31409000</v>
+        <v>40268000</v>
       </c>
       <c r="AB4" t="n">
-        <v>13873000</v>
+        <v>14475000</v>
       </c>
       <c r="AC4" t="n">
-        <v>429465000</v>
+        <v>-616249000</v>
       </c>
       <c r="AD4" t="n">
-        <v>835577000</v>
+        <v>405497000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-406112000</v>
+        <v>-1021746000</v>
       </c>
       <c r="AF4" t="n">
-        <v>77740000</v>
+        <v>184921000</v>
       </c>
       <c r="AG4" t="n">
-        <v>159882000</v>
+        <v>262340000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-82142000</v>
+        <v>-77419000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-15536000</v>
+        <v>-13678000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-15536000</v>
+        <v>-13678000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-65676000</v>
+        <v>-16046000</v>
       </c>
       <c r="AL4" t="n">
-        <v>3856000</v>
+        <v>14906000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-69532000</v>
+        <v>-30952000</v>
       </c>
       <c r="AN4" t="n">
-        <v>852933000</v>
+        <v>1102878000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-313635000</v>
+        <v>-359795000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-41751000</v>
+        <v>-96014000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>28932000</v>
+        <v>-87969000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-39875000</v>
+        <v>-17351000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-1663000</v>
+        <v>7154000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-29145000</v>
+        <v>2152000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-8715000</v>
+        <v>-9949000</v>
       </c>
       <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="n">
-        <v>155953000</v>
+        <v>166609000</v>
       </c>
       <c r="AX4" t="n">
-        <v>15299000</v>
+        <v>18730000</v>
       </c>
       <c r="AY4" t="n">
-        <v>140654000</v>
+        <v>147879000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-30574000</v>
+        <v>-39667000</v>
       </c>
       <c r="BA4" t="n">
-        <v>47000</v>
+        <v>-8648000</v>
       </c>
       <c r="BB4" t="n">
-        <v>-9242000</v>
+        <v>393000</v>
       </c>
       <c r="BC4" t="n">
-        <v>1092205000</v>
+        <v>1431554000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>816767000</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-71958000</v>
-      </c>
+        <v>629393000</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>-111160000</v>
+        <v>-200000000</v>
       </c>
       <c r="E5" t="n">
-        <v>5200000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>41830000</v>
-      </c>
+        <v>622000</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>-175602000</v>
+        <v>-79139000</v>
       </c>
       <c r="H5" t="n">
-        <v>1075606000</v>
+        <v>2056626000</v>
       </c>
       <c r="I5" t="n">
-        <v>1234022000</v>
+        <v>2295467000</v>
       </c>
       <c r="J5" t="n">
-        <v>-158416000</v>
+        <v>-238841000</v>
       </c>
       <c r="K5" t="n">
-        <v>-502485000</v>
+        <v>-1078214000</v>
       </c>
       <c r="L5" t="n">
-        <v>3490000</v>
+        <v>4746000</v>
       </c>
       <c r="M5" t="n">
-        <v>-3220000</v>
+        <v>-11548000</v>
       </c>
       <c r="N5" t="n">
-        <v>-214346000</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>-30128000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-71958000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>41830000</v>
-      </c>
+        <v>-720353000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-720353000</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>-105960000</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>-105960000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-111160000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>5200000</v>
-      </c>
+        <v>-199378000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-199378000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-200000000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>622000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>-648300000</v>
+        <v>130841000</v>
       </c>
       <c r="AA5" t="n">
-        <v>27131000</v>
+        <v>44078000</v>
       </c>
       <c r="AB5" t="n">
-        <v>17063000</v>
+        <v>15187000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-268723000</v>
+        <v>169296000</v>
       </c>
       <c r="AD5" t="n">
-        <v>927575000</v>
+        <v>547746000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-1196298000</v>
+        <v>-378450000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-256385000</v>
+        <v>-19685000</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-256385000</v>
+        <v>-19685000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-49399000</v>
+        <v>-1202000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-49399000</v>
+        <v>-1202000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-124937000</v>
+        <v>-76833000</v>
       </c>
       <c r="AL5" t="n">
-        <v>1266000</v>
+        <v>1104000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-126203000</v>
+        <v>-77937000</v>
       </c>
       <c r="AN5" t="n">
-        <v>992369000</v>
+        <v>708532000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-271278000</v>
+        <v>-399869000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-42703000</v>
+        <v>23237000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>17870000</v>
+        <v>-31464000</v>
       </c>
       <c r="AR5" t="n">
-        <v>13238000</v>
+        <v>5131000</v>
       </c>
       <c r="AS5" t="n">
-        <v>-8070000</v>
+        <v>-3800000</v>
       </c>
       <c r="AT5" t="n">
-        <v>-65741000</v>
+        <v>53370000</v>
       </c>
       <c r="AU5" t="n">
-        <v>-7623000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
+        <v>-5389000</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="n">
-        <v>146734000</v>
+        <v>173179000</v>
       </c>
       <c r="AX5" t="n">
-        <v>9318000</v>
+        <v>21729000</v>
       </c>
       <c r="AY5" t="n">
-        <v>137416000</v>
+        <v>151450000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-27966000</v>
+        <v>-44753000</v>
       </c>
       <c r="BA5" t="n">
-        <v>572000</v>
+        <v>-5609000</v>
       </c>
       <c r="BB5" t="n">
         <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>1179235000</v>
+        <v>810509000</v>
       </c>
     </row>
   </sheetData>
@@ -3482,7 +3482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FC2"/>
+  <dimension ref="A1:FE2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3938,345 +3938,355 @@
       </c>
       <c r="CM1" t="inlineStr">
         <is>
+          <t>recommendationMean</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr">
+        <is>
           <t>recommendationKey</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>numberOfAnalystOpinions</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>totalCash</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>totalCashPerShare</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>totalDebt</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>quickRatio</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>currentRatio</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>totalRevenue</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>debtToEquity</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>revenuePerShare</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>returnOnAssets</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>returnOnEquity</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>grossProfits</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>freeCashflow</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>operatingCashflow</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>revenueGrowth</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EX1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EY1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EZ1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="FA1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
+      <c r="FB1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="EQ1" t="inlineStr">
+      <c r="FC1" t="inlineStr">
         <is>
           <t>epsForward</t>
         </is>
       </c>
-      <c r="ER1" t="inlineStr">
+      <c r="FD1" t="inlineStr">
         <is>
           <t>epsCurrentYear</t>
         </is>
       </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EX1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EY1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EZ1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="FA1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="FB1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="FC1" t="inlineStr">
+      <c r="FE1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4358,7 +4368,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Xiaojiang  Bai', 'age': 67, 'title': 'Executive Chairman', 'yearBorn': 1958, 'fiscalYear': 2024, 'totalPay': 5232679, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Man  Ho CPA, CFA', 'age': 56, 'title': 'Chief Development Strategist &amp; Executive Director', 'yearBorn': 1969, 'fiscalYear': 2024, 'totalPay': 278026, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jianting  Ma', 'age': 44, 'title': 'CFO, Co-CEO', 'yearBorn': 1981, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Leiyi  Jin', 'age': 50, 'title': 'Co-Chief Executive Officer', 'yearBorn': 1975, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ching Kit  Cheng A.C.I.S., A.C.S.', 'age': 36, 'title': 'Joint Company Secretary', 'yearBorn': 1989, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Qiming  Zhu', 'age': 36, 'title': 'Joint Company Secretary', 'yearBorn': 1989, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Xiaojiang  Bai', 'age': 67, 'title': 'Executive Chairman', 'yearBorn': 1958, 'fiscalYear': 2024, 'totalPay': 5228509, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Man  Ho CPA, CFA', 'age': 56, 'title': 'Chief Development Strategist &amp; Executive Director', 'yearBorn': 1969, 'fiscalYear': 2024, 'totalPay': 277804, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jianting  Ma', 'age': 44, 'title': 'CFO, Co-CEO', 'yearBorn': 1981, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Leiyi  Jin', 'age': 50, 'title': 'Co-Chief Executive Officer', 'yearBorn': 1975, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ching Kit  Cheng A.C.I.S., A.C.S.', 'age': 36, 'title': 'Joint Company Secretary', 'yearBorn': 1989, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Qiming  Zhu', 'age': 36, 'title': 'Joint Company Secretary', 'yearBorn': 1989, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -4377,7 +4387,7 @@
         <v>9</v>
       </c>
       <c r="V2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="W2" t="n">
         <v>1735603200</v>
@@ -4433,10 +4443,10 @@
         <v>3.17</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.658</v>
+        <v>0.662</v>
       </c>
       <c r="AO2" t="n">
-        <v>12.057729</v>
+        <v>12.064225</v>
       </c>
       <c r="AP2" t="n">
         <v>10900000</v>
@@ -4445,7 +4455,7 @@
         <v>10900000</v>
       </c>
       <c r="AR2" t="n">
-        <v>4074104</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
         <v>0</v>
@@ -4475,7 +4485,7 @@
         <v>2.51</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="BC2" t="n">
         <v>9.58</v>
@@ -4490,7 +4500,7 @@
         <v>2.64</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.8168</v>
+        <v>2.7728</v>
       </c>
       <c r="BH2" t="n">
         <v>0.154</v>
@@ -4522,16 +4532,16 @@
         <v>0.44674</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.14715</v>
+        <v>0.14239</v>
       </c>
       <c r="BR2" t="n">
         <v>2271063422</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.188888</v>
+        <v>2.1877265</v>
       </c>
       <c r="BT2" t="n">
-        <v>1.2060919</v>
+        <v>1.2067323</v>
       </c>
       <c r="BU2" t="n">
         <v>1735603200</v>
@@ -4549,7 +4559,7 @@
         <v>-0.1</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.21894671</v>
+        <v>0.21882881</v>
       </c>
       <c r="CA2" t="n">
         <v>2.876</v>
@@ -4558,10 +4568,10 @@
         <v>10.482</v>
       </c>
       <c r="CC2" t="n">
-        <v>-0.28065395</v>
+        <v>-0.27472526</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="CE2" t="n">
         <v>0.07000000000000001</v>
@@ -4578,262 +4588,270 @@
         <v>2.64</v>
       </c>
       <c r="CI2" t="n">
-        <v>4.3212047</v>
+        <v>4.199978</v>
       </c>
       <c r="CJ2" t="n">
-        <v>3.0735006</v>
+        <v>3.0687253</v>
       </c>
       <c r="CK2" t="n">
-        <v>3.5384412</v>
+        <v>3.4947727</v>
       </c>
       <c r="CL2" t="n">
-        <v>3.22063</v>
-      </c>
-      <c r="CM2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="CN2" t="n">
+        <v>3.215626</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>1.66667</v>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="CO2" t="n">
         <v>3</v>
       </c>
-      <c r="CO2" t="n">
+      <c r="CP2" t="n">
         <v>2105872000</v>
       </c>
-      <c r="CP2" t="n">
+      <c r="CQ2" t="n">
         <v>0.927</v>
       </c>
-      <c r="CQ2" t="n">
+      <c r="CR2" t="n">
         <v>435823008</v>
       </c>
-      <c r="CR2" t="n">
+      <c r="CS2" t="n">
         <v>104332000</v>
       </c>
-      <c r="CS2" t="n">
+      <c r="CT2" t="n">
         <v>1.426</v>
       </c>
-      <c r="CT2" t="n">
+      <c r="CU2" t="n">
         <v>1.829</v>
       </c>
-      <c r="CU2" t="n">
+      <c r="CV2" t="n">
         <v>1588343040</v>
       </c>
-      <c r="CV2" t="n">
+      <c r="CW2" t="n">
         <v>2.144</v>
       </c>
-      <c r="CW2" t="n">
+      <c r="CX2" t="n">
         <v>0.699</v>
       </c>
-      <c r="CX2" t="n">
+      <c r="CY2" t="n">
         <v>0.02261</v>
       </c>
-      <c r="CY2" t="n">
+      <c r="CZ2" t="n">
         <v>-0.02227</v>
       </c>
-      <c r="CZ2" t="n">
+      <c r="DA2" t="n">
         <v>947966016</v>
       </c>
-      <c r="DA2" t="n">
+      <c r="DB2" t="n">
         <v>970417280</v>
       </c>
-      <c r="DB2" t="n">
+      <c r="DC2" t="n">
         <v>426921984</v>
       </c>
-      <c r="DC2" t="n">
+      <c r="DD2" t="n">
         <v>-0.445</v>
       </c>
-      <c r="DD2" t="n">
+      <c r="DE2" t="n">
         <v>0.59683</v>
       </c>
-      <c r="DE2" t="n">
+      <c r="DF2" t="n">
         <v>0.27438998</v>
       </c>
-      <c r="DF2" t="n">
+      <c r="DG2" t="n">
         <v>-0.01901</v>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DH2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DI2" t="inlineStr">
         <is>
           <t>1448.HK</t>
         </is>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DJ2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="DK2" t="inlineStr">
+      <c r="DL2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="DL2" t="inlineStr">
+      <c r="DM2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="DM2" t="b">
+      <c r="DN2" t="b">
         <v>0</v>
       </c>
-      <c r="DN2" t="inlineStr">
+      <c r="DO2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="DO2" t="b">
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DR2" t="n">
         <v>0</v>
       </c>
-      <c r="DP2" t="n">
+      <c r="DS2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>16.824932</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>-0.13279986</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>-0.047893777</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>1.7 - Buy</t>
+        </is>
+      </c>
+      <c r="EB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>1773907693</v>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>finmb_252538129</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="EH2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="EJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EL2" t="n">
         <v>1387416600000</v>
       </c>
-      <c r="DQ2" t="inlineStr">
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>Fu Shou Yuan International Group Limited</t>
+        </is>
+      </c>
+      <c r="EN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>2.62 - 2.69</t>
+        </is>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="EQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>0.13000011</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>0.051792875</v>
+      </c>
+      <c r="ET2" t="inlineStr">
+        <is>
+          <t>2.51 - 3.81</t>
+        </is>
+      </c>
+      <c r="EU2" t="n">
+        <v>-1.1699998</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>-0.3070866</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>-27.472527</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>1742568613</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>1742568613</v>
+      </c>
+      <c r="EZ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="FA2" t="inlineStr">
         <is>
           <t>FU SHOU YUAN</t>
         </is>
       </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DS2" t="n">
-        <v>1773907693</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>finmb_252538129</t>
-        </is>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DX2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DZ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>PRE</t>
-        </is>
-      </c>
-      <c r="EB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>2.62 - 2.69</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="EF2" t="n">
-        <v>4074104</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>0.13000011</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>0.051792875</v>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>2.51 - 3.82</t>
-        </is>
-      </c>
-      <c r="EJ2" t="n">
-        <v>-1.1799998</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>-0.30890048</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>-28.065395</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>1742568613</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>1742568613</v>
-      </c>
-      <c r="EO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EP2" t="n">
+      <c r="FB2" t="n">
         <v>-0.1</v>
       </c>
-      <c r="EQ2" t="n">
-        <v>0.21894671</v>
-      </c>
-      <c r="ER2" t="n">
+      <c r="FC2" t="n">
+        <v>0.21882881</v>
+      </c>
+      <c r="FD2" t="n">
         <v>0.15691</v>
       </c>
-      <c r="ES2" t="n">
-        <v>16.824932</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>-0.17680001</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>-0.06276626</v>
-      </c>
-      <c r="EX2" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="EY2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EZ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="FA2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FB2" t="inlineStr">
-        <is>
-          <t>Fu Shou Yuan International Group Limited</t>
-        </is>
-      </c>
-      <c r="FC2" t="inlineStr"/>
+      <c r="FE2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
